--- a/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00981A/ETF_Investment_Portfolio_20260729.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>9.71%</t>
+          <t>9.86%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.14%</t>
+          <t>7.96%</t>
         </is>
       </c>
     </row>
@@ -682,29 +682,29 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.61%</t>
+          <t>5.31%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>16,971,000</t>
+          <t>2,417,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.14%</t>
+          <t>5.18%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.13%</t>
+          <t>5.05%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,417,000</t>
+          <t>2,443,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>5.10%</t>
+          <t>4.88%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,443,000</t>
+          <t>16,971,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>5.01%</t>
+          <t>4.87%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>4.82%</t>
+          <t>4.74%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.22%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>3.90%</t>
+          <t>3.70%</t>
         </is>
       </c>
     </row>
@@ -858,51 +858,51 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>3.69%</t>
+          <t>3.49%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>台達電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>16,327,000</t>
+          <t>5,567,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>3.59%</t>
+          <t>3.47%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>5,567,000</t>
+          <t>16,327,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>3.49%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
@@ -924,51 +924,51 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>3.13%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>信驊</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>7,478,000</t>
+          <t>448,900</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5274</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>信驊</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>448,900</t>
+          <t>7,478,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.28%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.20%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.02%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>349,000</t>
+          <t>319,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1122,24 +1122,24 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>亞德客-KY</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>1,682,000</t>
+          <t>528,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,88 +1151,88 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>亞德客-KY</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>528,000</t>
+          <t>1,682,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>頎邦</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>4,706,000</t>
+          <t>3,972,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.23%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>4,334,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.21%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>穎崴</t>
+          <t>頎邦</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>3,764,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,966,000</t>
+          <t>2,718,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1276,24 +1276,24 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.15%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>高技</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,586,000</t>
+          <t>3,988,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,66 +1305,66 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,988,000</t>
+          <t>1,741,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3376</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,741,000</t>
+          <t>1,508,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>高技</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>1,508,000</t>
+          <t>1,056,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>世界</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -1437,12 +1437,12 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>世界</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1503,12 +1503,12 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>美律</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>金居</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,12 +1547,12 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>高力</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -1569,12 +1569,12 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>南茂</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>美律</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>金居</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>高力</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -1701,12 +1701,12 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>8150</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>南茂</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>10,422,345,646</t>
+          <t>12,963,536,816</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
@@ -1769,7 +1769,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>2,738,436,376</t>
+          <t>3,044,555,541</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr"/>
